--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -431,26 +431,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{656C07E2-B43E-4AED-A01D-BAF0B393F7F0}">
-  <we:reference id="WA200010611" version="1.0.10036.0" store="en-us" storeType="OMEX"/>
-  <we:alternateReferences/>
-  <we:properties>
-    <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -546,7 +526,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>⬜ Not started</t>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1254,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1266,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1278,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1290,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1302,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1314,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1326,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1350,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1362,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Deferred — no forced displacement system yet</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1379,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -556,7 +556,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>⬜ Not started</t>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -1446,192 +1456,306 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skill Card UI: player sees available skills with MP cost and range</t>
+          <t>Player input system: client sends commands to server, server validates via CommandService</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PREREQUISITE — without this, all other Slice 3 items are untestable by the player</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Selecting a skill shows valid target tiles/units highlighted</t>
+          <t>Battle runs 3v3 (3 player units, 3 enemy units) to test timeline with multiple units</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PREREQUISITE — proves targeting, turn order, and AI with multiple units per side</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>At least one single-target damage skill works (e.g., Power Strike)</t>
+          <t>Skill Card UI: player sees available skills with MP cost and range</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>At least one AOE skill works (e.g., Line or Cleave pattern)</t>
+          <t>Selecting a skill shows valid target tiles/units highlighted</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>At least one support/healing skill works</t>
+          <t>At least one single-target damage skill works (e.g., Power Strike)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MP cost deducted on use; can't use if MP too low</t>
+          <t>At least one AOE skill works (e.g., Line or Cleave pattern)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skill RT cost applied correctly (different from Basic Attack RT)</t>
+          <t>At least one support/healing skill works</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skill Power formula calculates correctly (weapon + stat scaling)</t>
+          <t>MP cost deducted on use; can't use if MP too low</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>At least 2 status effects: Poison (DoT) and Burn (DoT + spread)</t>
+          <t>Skill RT cost applied correctly (different from Basic Attack RT)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Status duration ticks down correctly</t>
+          <t>Skill Power formula calculates correctly (weapon + stat scaling)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Status damage applies at correct timing</t>
+          <t>At least 2 status effects: Poison (DoT) and Burn (DoT + spread)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Status visual indicator on affected units</t>
+          <t>Status duration ticks down correctly</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Channel Time works: skill with channel shows delay before activating</t>
+          <t>Status damage applies at correct timing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trigger safety: on-hit effects fire once per target, no loops</t>
+          <t>Status visual indicator on affected units</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enemy AI uses skills (not just Basic Attack)</t>
+          <t>Channel Time works: skill with channel shows delay before activating</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Trigger safety: on-hit effects fire once per target, no loops</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Enemy AI uses skills (not just Basic Attack)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Enemy AI picks appropriate skill (heal if low HP, attack otherwise)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>⬜</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 5 - Procedural Maps" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 6 - Content Expansion" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 7 - Visual Polish" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -627,6 +628,274 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>⬜ Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Visual Polish</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Visual/audio pass: terrain, animations, VFX, UI, camera, sound</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>⬜ Not Started</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Goal:</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Make the game look and feel good — terrain materials, props, lighting, animations, UI polish, camera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Done When:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A new player watches 30 seconds of gameplay and it looks like a real game, not a prototype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Terrain tiles have distinct materials per type (grass, stone, sand, water, etc.)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Elevation visually reads clearly (cliff faces, ramps, height layers)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Each biome has a unique visual palette and props</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Map props/objects placed (trees, rocks, buildings, fences)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lighting per biome (warm plains, cold highlands, dark caves)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Unit models distinct per weapon archetype or role</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Attack animations (swing, thrust, cast, shoot)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Skill VFX (fire burst, heal glow, poison cloud, etc.)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Status effect visual indicators on units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CT timeline bar UI (Mana Khemia style, top of screen)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Skill Card selection UI polished</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Damage/healing numbers styled (floating, color-coded)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Camera system (follow active unit, smooth transitions)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Menu/loadout UI visual design</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sound effects (hit, heal, status apply, UI clicks)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Music per biome or battle phase</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
     </row>
@@ -1770,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -1998,6 +2267,114 @@
           <t>⬜</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>--- Persistent HP/MP (bundled into Slice 4) ---</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UnitSchema accepts persistent HP/MP instead of defaulting to full</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pass currentHp/currentMp from save state</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MP Regen system: accumulator + CT-based tick</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GameConstants + BattleCoordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Battle-end: persist final HP/MP + apply 35% recovery</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Main.server.lua hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Battle-start: load persistent HP/MP from save state</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Main.server.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KO units get zero recovery, flagged in save</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Deployment UI shows current HP/MP before battle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prior Work" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 1 - Flat Board" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 2 - Terrain Height" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 3 - Skills Combat" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 4 - Loadouts Saving" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 5 - Procedural Maps" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 6 - Content Expansion" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 7 - Visual Polish" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Development Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prior Work" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 1 - Flat Board" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 2 - Terrain Height" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 3 - Skills Combat" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 4 - Loadouts Saving" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 5 - Procedural Maps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 6 - Content Expansion" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 7 - Visual Polish" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +648,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>⬜ Not Started</t>
+          <t>🔄 In Progress — Stage 1 Desktop Checkpoint Verified</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -662,7 +668,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marking progress</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Change ⬜ to ✅ in the Status column when a task is working in Roblox Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Updating overview</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>When all items in a slice are ✅, update Status Overview and fill in the Completed date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Starting new session</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tell AI: "Read my game docs in D:\AI\Projects\CTRBLXAI\docs. Check the roadmap for where I am."</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>One slice = multiple sessions</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Each slice may take many chat sessions. That's normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Order matters</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Don't skip ahead. Later slices depend on earlier ones working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Notes column</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Track issues, decisions, or things to revisit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,7 +781,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Make the game look and feel good — terrain materials, props, lighting, animations, UI polish, camera.</t>
+          <t>VISUALS, LAYOUT, THEMES, ASSETS, AND PRESENTATION — make the game look and feel good</t>
         </is>
       </c>
     </row>
@@ -685,7 +793,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A new player watches 30 seconds of gameplay and it looks like a real game, not a prototype.</t>
+          <t>A new player watches 30 seconds of gameplay and it looks like a real game, not a prototype. All visual work consumes authoritative data from other slices.</t>
         </is>
       </c>
     </row>
@@ -859,7 +967,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄 Desktop Verified</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Stage 1 Desktop Checkpoint. Commit: e8dcc977. Mobile pending.</t>
         </is>
       </c>
     </row>
@@ -896,6 +1009,956 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>═══ STAGE 1: TACTICAL CAMERA ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- Desktop Checkpoint (VERIFIED) ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Commit: e8dcc9774d494f86d7c44be3fec994fbdef6ec63</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tactical camera fixed pitch: 50 degrees</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tactical camera fixed FieldOfView: 55 degrees</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Camera distances: Min 38, Default 53, Max 96 studs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Playable battle-grid bounds: X -20..20, Z -20..20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Two-tile camera pan margin</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Screen-relative WASD panning</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Screen-relative arrow-key panning</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Diagonal movement normalization</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Desktop right-drag camera panning</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q/E rotation in fixed 45-degree steps</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mouse-wheel zoom</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Left-click tile selection</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HUD panels block battlefield clicks</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HUD panels block camera drags</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Focus Active camera recovery</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Reset Camera recovery</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Battle-only tactical camera activation</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Desktop bootstrap after declaration-order correction</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Studio-only DEV CAMERA TEST panel</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>--- Mobile Validation (PENDING) ---</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Studio Emulator two-finger mode issue; not a confirmed code failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mobile single-tap tile selection</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pending reliable single-touch UAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Mobile single-finger camera pan</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mobile two-finger fixed-angle rotation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Mobile pinch zoom</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Mobile gesture input blocking</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>--- Deferred to Slice 7 View Mode ---</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Focus Selected camera integration</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BattleHUD resolves to active unit, not separately inspected unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Independent inspected-unit state</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>--- Parked Visual/Tuning ---</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Right-drag sensitivity tuning</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Grid readability at yaw 0 and 90 degrees</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rotated/zoomed visible-footprint camera tuning</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TemplateInspector white selection outline</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Startup avatar and native-control flash</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Future battle-entry cinematic</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Production camera-recovery buttons</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>--- Separately Tracked Defects (not camera scope) ---</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>🐛</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Attack confirmation regression</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>🐛</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tracked separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BoardClient ReplicatedStorage.Modules error</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>🐛</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tracked separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UIController initial viewport reported as 1x1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>🐛</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tracked separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>═══ SLICE 7 CROSS-SLICE BOUNDARY ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Slice 7 MAY define and implement:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Client visual composition and layout</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Battle UI phase display (consumes phase state from server, does not own transitions)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  View Mode visual presentation (consumes inspected-unit data, does not own selection state)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Camera presentation and input forwarding (does not own battle-input mode)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Responsive layout</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Visual asset lookup and fallback behavior</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Display contracts for preview, timeline, status, log, unit, tile, object, and battlefield-condition data</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Slice 7 MUST NOT define or modify:</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Combat formulas</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Action legality</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Movement legality</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Target legality</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CT or RT calculations</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Status behavior</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Weather behavior</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Crisis behavior</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Time progression rules</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Event scheduling rules</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Summon-duration rules</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Object interaction rules</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Server-authoritative action results</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Database content</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Fallback rule: When required presentation data is unavailable, report the missing field and render a safe fallback or omit the field. Do not calculate authoritative values on the client to complete a panel.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VISUALS, LAYOUT, THEMES, ASSETS, AND PRESENTATION ONLY. UI composition, responsive layout, theme/colors/typography, portraits/icons/models, terrain materials, prop visuals, lighting, animations, VFX, floating numbers, timeline appearance, battle log appearance, camera presentation, audio, missing-asset fallbacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BattleHUD.lua, Theme.lua, UIConstants.lua, UIFormatting.lua, UIComponents.lua, UILayoutCoordinator.lua, UIController.client.lua, UnitInspectorPanel.client.lua, CameraController.lua (camera/presentation only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BattleVisualClient.client.lua (read only — presentation hooks require approval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>All slices (consumes their public events and APIs for display)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Visual rendering, user input intent (forwarded to server), display fallbacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Battle phase state, active unit, targets, preview values, timeline, status, inventory, equipment, map state — all as read-only display data</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Must not modify: combat formulas, movement/target legality, CT/RT, command validation, skill/status resolution, timeline ordering, save/load, inventory/equipment transactions, recruitment/tavern/blacksmith/quest logic, map generation, content definitions, CTRBLXAI.db</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Minimum cross-slice smoke test + focused camera regression for camera changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>🔄 In Progress — Stage 1 Desktop Checkpoint: e8dcc977</t>
         </is>
       </c>
     </row>
@@ -905,6 +1968,463 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SLICE DEVELOPMENT MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A slice is a broad player-facing development milestone handled in a dedicated AI conversation where practical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Each slice owns a defined group of modules. When completed: behavior verified, public APIs recorded, internals protected, Git checkpoint recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Later slices consume APIs instead of rewriting internals. Completed slices are not permanently immutable — backward-compatible additions may be approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FOUR MODULE CLASSIFICATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Slice-Owned</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Modules primarily owned by one slice</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Owning slice modifies normally. After completion, later slices consume through public APIs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Protected Completed</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Modules belonging to a completed slice</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Later slices: read, require, consume events. Must not rewrite internals for convenience, style, cleanup, or refactoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Shared Integration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Modules where multiple systems meet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Every modification requires: exact purpose, smallest diff, no unrelated cleanup, explicit approval, regression test, Git checkpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Content/Config Authority</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CTRBLXAI.db, skill/weapon/status definitions, templates</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rule ownership in Game Rules. Presentation slices must not change gameplay values to make a screen easier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CROSS-SLICE COMPATIBILITY PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Identify exact missing API, event, callback, or data field</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Identify owning slice and module</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Determine if existing API or visual fallback works</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Do NOT duplicate formula, validation, state, or data</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>If no fallback, produce a compatibility request</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Obtain explicit developer approval before editing protected/shared module</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Apply smallest backward-compatible interface addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Do not change existing authoritative behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Run owning slice's minimum regression test</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Commit compatibility change before continuing requesting slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Record as compatibility addition — ownership does NOT transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DEPENDENCY DIRECTION (preferred)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Authoritative rules/content → gameplay services → shared events/payloads → functional client controllers → presentation adapters/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Forbidden: combat services requiring UI, map gen requiring visual layout, save services reading UI state, gameplay formulas depending on presentation assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MINIMUM CROSS-SLICE SMOKE TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>After every verified phase touching UI, shared client, or battle presentation:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1. Battle starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2. Expected units appear</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3. First player turn begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4. Movement reaches confirmation/execution path</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5. Basic Attack reaches targeting and execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6. One Skill targets and resolves</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7. Next action or turn begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8. UI input does not trigger battlefield actions behind panels</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9. No new causal runtime error in Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RISK-BASED WORKFLOW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Theme, colors, typography, spacing, panel positions, assets, VFX, audio</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Inspect → implement → sanity check → visual UAT → smoke test → commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Medium Risk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Shared client events, presentation adapters, responsive reflow, camera integration</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Impact check → smallest change → focused audit → focused UAT → smoke test → commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Combat formulas, target legality, CT/RT, save data, inventory, map gen, server payloads</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Compatibility request → approval → focused impl → owning-slice regression → integration test → commit</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1230,13 +2750,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -1453,212 +2973,118 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Goal:</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Same battle, but board has hills, mud, walls. Height matters. Mud slows you. High ground gives damage bonus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Done When:</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Battle on uneven terrain plays correctly. Units path around walls, slow on mud, benefit from high ground. AI navigates properly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Grid tiles have elevation values (0, 1, 2, 3)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Visual difference between elevation levels</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jump stat works: unit can only climb ≤ Jump per step</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Downward Jump works: can drop Jump + 2 voluntarily</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>At least 3 terrain types rendered (Clear, Grassland, Mud)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Terrain cost applies: Mud = 2, Clear/Grassland = 1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Movement range accounts for terrain cost correctly</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Blocking objects placed (rocks/walls can't be walked through)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Elevation damage bonus works: higher attacker deals more</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Elevation defense bonus works: lower attacker deals less</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fall damage works: forced off a height → takes damage</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>⏭️</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Deferred — no forced displacement system yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI navigates around obstacles and considers terrain cost</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>✅</t>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Core battle lifecycle, CT/RT progression, ready units/turns, AP turns, basic Move + Basic Attack flow, basic AI, KO, victory/defeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BattleCoordinator.lua, UnitSchema.lua, GameConstants.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Main.server.lua, BattleEvents.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>None (first slice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Battle lifecycle events, unit turn results, CT/RT advancement, KO/victory/defeat signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Later slices must not change CT, RT, KO, victory, defeat, or turn progression without a compatibility request</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Battle starts, units take turns, Basic Attack resolves, KO triggers, victory fires once</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Completed 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1668,372 +3094,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Goal:</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Units have 2-3 skills. Pick a skill, select target area, confirm. Status effects tick. Combat feels like a real tactics game.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Done When:</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3v3 battle with skills and statuses feels like a real tactical RPG. Poison ticks, AOE hits, healing works, AI makes reasonable choices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Player input system: client sends commands to server, server validates via CommandService</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PREREQUISITE — without this, all other Slice 3 items are untestable by the player</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Battle runs 3v3 (3 player units, 3 enemy units) to test timeline with multiple units</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PREREQUISITE — proves targeting, turn order, and AI with multiple units per side</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Skill Card UI: player sees available skills with MP cost and range</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Selecting a skill shows valid target tiles/units highlighted</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>At least one single-target damage skill works (e.g., Power Strike)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>At least one AOE skill works (e.g., Line or Cleave pattern)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>At least one support/healing skill works</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MP cost deducted on use; can't use if MP too low</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Skill RT cost applied correctly (different from Basic Attack RT)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Skill Power formula calculates correctly (weapon + stat scaling)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>At least 2 status effects: Poison (DoT) and Burn (DoT + spread)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Status duration ticks down correctly</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Status damage applies at correct timing</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Status visual indicator on affected units</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Channel Time works: skill with channel shows delay before activating</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Trigger safety: on-hit effects fire once per target, no loops</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Enemy AI uses skills (not just Basic Attack)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Already working from Slice 2 implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Enemy AI picks appropriate skill (heal if low HP, attack otherwise)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Verified in source code audit 2026-08-23</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2055,7 +3115,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Win battle → get loot. Go to menu, equip it. Save. Close Roblox, reopen — everything still there.</t>
+          <t>Same battle, but board has hills, mud, walls. Height matters. Mud slows you. High ground gives damage bonus.</t>
         </is>
       </c>
     </row>
@@ -2067,7 +3127,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Play multiple battles, collect loot, equip gear, save, close, reopen — progress intact. Different weapons change combat.</t>
+          <t>Battle on uneven terrain plays correctly. Units path around walls, slow on mud, benefit from high ground. AI navigates properly.</t>
         </is>
       </c>
     </row>
@@ -2091,290 +3151,747 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Battle end → reward screen shows loot (1-2 items)</t>
+          <t>Grid tiles have elevation values (0, 1, 2, 3)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Item generation works: rarity, random stat bonuses, BP validation</t>
+          <t>Visual difference between elevation levels</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Items appear in inventory</t>
+          <t>Jump stat works: unit can only climb ≤ Jump per step</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Menu UI: player can view roster of units</t>
+          <t>Downward Jump works: can drop Jump + 2 voluntarily</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Menu UI: player can view inventory of items</t>
+          <t>At least 3 terrain types rendered (Clear, Grassland, Mud)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Player can equip a weapon → unit stats change</t>
+          <t>Terrain cost applies: Mud = 2, Clear/Grassland = 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Equipment affects combat: different weapon = different damage/WT/range</t>
+          <t>Movement range accounts for terrain cost correctly</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Weapon WT applies to Basic Attack RT correctly</t>
+          <t>Blocking objects placed (rocks/walls can't be walked through)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Save writes to Roblox DataStore (compact numeric format)</t>
+          <t>Elevation damage bonus works: higher attacker deals more</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Load reads from DataStore and rebuilds full state</t>
+          <t>Elevation defense bonus works: lower attacker deals less</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Save survives closing and reopening the game</t>
+          <t>Fall damage works: forced off a height → takes damage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Deferred — no forced displacement system yet</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Save split: roster in key 1, inventory in key 2</t>
+          <t>AI navigates around obstacles and considers terrain cost</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Terrain movement, elevation, Jump, movement pathing, blocking, target geometry, range, battlefield legality</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TargetingService.lua, TileDefinitions.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Main.server.lua, GameConstants.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Slice 1 (battle lifecycle, turn system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Movement candidates, target candidates, range validation, elevation data, Jump/pathing APIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Slice 1 battle lifecycle, unit state</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Later slices may display movement/target candidates but must not recalculate them</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Movement respects terrain cost, elevation blocks correctly, Jump works, range validates</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Completed 2026-08-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Goal:</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Units have 2-3 skills. Pick a skill, select target area, confirm. Status effects tick. Combat feels like a real tactics game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Done When:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3v3 battle with skills and statuses feels like a real tactical RPG. Poison ticks, AOE hits, healing works, AI makes reasonable choices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Player input system: client sends commands to server, server validates via CommandService</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PREREQUISITE — without this, all other Slice 3 items are untestable by the player</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Battle runs 3v3 (3 player units, 3 enemy units) to test timeline with multiple units</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PREREQUISITE — proves targeting, turn order, and AI with multiple units per side</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Skill Card UI: player sees available skills with MP cost and range</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Selecting a skill shows valid target tiles/units highlighted</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>At least one single-target damage skill works (e.g., Power Strike)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>At least one AOE skill works (e.g., Line or Cleave pattern)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>At least one support/healing skill works</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MP cost deducted on use; can't use if MP too low</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Skill RT cost applied correctly (different from Basic Attack RT)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Skill Power formula calculates correctly (weapon + stat scaling)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>At least 2 status effects: Poison (DoT) and Burn (DoT + spread)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Status duration ticks down correctly</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lookup table approach: save stores IDs, game resolves to full data</t>
+          <t>Status damage applies at correct timing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Doctrine equip works: stat package applies</t>
+          <t>Status visual indicator on affected units</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>At least 3 weapon types feel different (Sword, Spear, Bow)</t>
+          <t>Channel Time works: skill with channel shows delay before activating</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Trigger safety: on-hit effects fire once per target, no loops</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- Persistent HP/MP (bundled into Slice 4) ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+          <t>Enemy AI uses skills (not just Basic Attack)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Already working from Slice 2 implementation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UnitSchema accepts persistent HP/MP instead of defaulting to full</t>
+          <t>Enemy AI picks appropriate skill (heal if low HP, attack otherwise)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pass currentHp/currentMp from save state</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MP Regen system: accumulator + CT-based tick</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GameConstants + BattleCoordinator</t>
+          <t>Verified in source code audit 2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Battle-end: persist final HP/MP + apply 35% recovery</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Main.server.lua hook</t>
+          <t>═══ SLICE OWNERSHIP ═══</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Battle-start: load persistent HP/MP from save state</t>
+          <t>Functional Scope</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Main.server.lua</t>
+          <t>Client command submission, server command validation, Skills, AOE/patterns, MP/action costs, statuses, channeling/activation, combat resolution, trigger safety, skill-using AI, Guard</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KO units get zero recovery, flagged in save</t>
+          <t>Owned Module Group</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>CommandService.lua, CombatResolver.lua, StatusService.lua</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deployment UI shows current HP/MP before battle</t>
+          <t>Shared Integration Modules</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Main.server.lua, BattleEvents.lua, BattleVisualBroadcaster.lua, GameConstants.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Slice 1 (battle lifecycle), Slice 2 (targeting, range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Command validation results, damage/healing outcomes, status application events, skill resolution pipeline, Guard mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Slice 1 turn system, Slice 2 targeting/range</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Slice 7 may present these but must not own transitions, validation, or calculations</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Skill spends MP, channeling completes/interrupts, Poison/Burn tick, AOE resolves, Guard mitigates, AI uses skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Completed 2026-08-23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2387,7 +3904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -2403,7 +3920,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Game generates a random map before battle. Different every time. Always playable. One biome + one template.</t>
+          <t>Win battle → get loot. Go to menu, equip it. Save. Close Roblox, reopen — everything still there.</t>
         </is>
       </c>
     </row>
@@ -2415,7 +3932,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Every battle has a different but valid map. No broken maps, no freeze, no unreachable enemies.</t>
+          <t>Play multiple battles, collect loot, equip gear, save, close, reopen — progress intact. Different weapons change combat.</t>
         </is>
       </c>
     </row>
@@ -2439,7 +3956,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Map generation runs on the server (not client)</t>
+          <t>Battle end → reward screen shows loot (1-2 items)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2451,7 +3968,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Seed-based: same seed → same map (deterministic)</t>
+          <t>Item generation works: rarity, random stat bonuses, BP validation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2463,7 +3980,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Plains biome profile loads terrain weights correctly</t>
+          <t>Items appear in inventory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2475,7 +3992,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T01 Frontline Pressure template places PD, ED, LAN zones</t>
+          <t>Menu UI: player can view roster of units</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2487,7 +4004,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Terrain fills grid based on biome weights</t>
+          <t>Menu UI: player can view inventory of items</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2499,7 +4016,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regions form (connected groups of similar terrain)</t>
+          <t>Player can equip a weapon → unit stats change</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2511,7 +4028,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Elevation assigned consistent with biome profile</t>
+          <t>Equipment affects combat: different weapon = different damage/WT/range</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2523,7 +4040,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Connectivity validation: player can reach enemies via LAN</t>
+          <t>Weapon WT applies to Basic Attack RT correctly</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2535,7 +4052,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Objects placed without blocking required paths</t>
+          <t>Save writes to Roblox DataStore (compact numeric format)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2547,7 +4064,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>If generation fails → retry (up to 3 attempts)</t>
+          <t>Load reads from DataStore and rebuilds full state</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2559,7 +4076,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Generation completes within 2 seconds</t>
+          <t>Save survives closing and reopening the game</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2571,7 +4088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Frame yielding: no visible freeze during generation</t>
+          <t>Save split: roster in key 1, inventory in key 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2583,7 +4100,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Generated map renders correctly in Roblox Studio</t>
+          <t>Lookup table approach: save stores IDs, game resolves to full data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2595,7 +4112,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pre-generation: map ready before player enters battle</t>
+          <t>Doctrine equip works: stat package applies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2607,12 +4124,226 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>All Slice 1-4 systems work on the generated map</t>
+          <t>At least 3 weapon types feel different (Sword, Spear, Bow)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>--- Persistent HP/MP (bundled into Slice 4) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UnitSchema accepts persistent HP/MP instead of defaulting to full</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pass currentHp/currentMp from save state</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MP Regen system: accumulator + CT-based tick</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GameConstants + BattleCoordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Battle-end: persist final HP/MP + apply 35% recovery</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Main.server.lua hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Battle-start: load persistent HP/MP from save state</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Main.server.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KO units get zero recovery, flagged in save</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Deployment UI shows current HP/MP before battle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Persistent roster, inventory, equipment, core loadouts, Skill/Doctrine/Augment assignment, deployment, save/load, DataStore, persistent HP/MP, post-battle recovery, battle rewards, item generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SaveService.lua, PersistentStateService.lua, InventoryService.lua, EquipmentService.lua, ItemGenerator.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Main.server.lua, BattleEvents.lua, UnitSchema.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Slices 1-3 (battle lifecycle, combat, targeting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Save/load API, inventory state, equipment profiles, deployment roster, persistent HP/MP, item generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Slices 1-3 battle results, unit state, combat outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Slice 7 may provide visual components but must not own inventory, equipment, loadout, or save transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Equip changes stats, save persists, load rebuilds, item generation validates BP band, post-battle recovery applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>⬜ In Progress</t>
         </is>
       </c>
     </row>
@@ -2627,7 +4358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -2643,7 +4374,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Fill with all designed content. Systems work — this is volume and variety.</t>
+          <t>Game generates a random map before battle. Different every time. Always playable. One biome + one template.</t>
         </is>
       </c>
     </row>
@@ -2655,7 +4386,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20+ battles without repeating. Biomes feel distinct. Different builds create different playstyles.</t>
+          <t>Every battle has a different but valid map. No broken maps, no freeze, no unreachable enemies.</t>
         </is>
       </c>
     </row>
@@ -2679,7 +4410,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All 15 Races implemented with passives and growth rates</t>
+          <t>Map generation runs on the server (not client)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2691,7 +4422,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>All 15 Doctrines implemented with stat packages and skills</t>
+          <t>Seed-based: same seed → same map (deterministic)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2703,7 +4434,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Skill catalog loaded (all entries from Game Rules)</t>
+          <t>Plains biome profile loads terrain weights correctly</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2715,7 +4446,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Augment catalog loaded (all Active entries)</t>
+          <t>T01 Frontline Pressure template places PD, ED, LAN zones</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2727,7 +4458,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>All conventional weapon archetypes (15 types)</t>
+          <t>Terrain fills grid based on biome weights</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2739,7 +4470,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>All status effects (damage, control, buff/state)</t>
+          <t>Regions form (connected groups of similar terrain)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2751,7 +4482,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>All 8 templates (T01-T08) for map generation</t>
+          <t>Elevation assigned consistent with biome profile</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2763,7 +4494,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>All biomes (Plains through Beach — 12 total)</t>
+          <t>Connectivity validation: player can reach enemies via LAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2775,7 +4506,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>All terrain types with transformations working</t>
+          <t>Objects placed without blocking required paths</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2787,7 +4518,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>All map objects with interactions</t>
+          <t>If generation fails → retry (up to 3 attempts)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2799,7 +4530,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Encounter generation: different enemies per biome</t>
+          <t>Generation completes within 2 seconds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2811,7 +4542,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Battle conditions active (Rain, Thunderstorm, Heatwave, etc.)</t>
+          <t>Frame yielding: no visible freeze during generation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2823,7 +4554,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Loot tables tuned per source (Normal, Elite, Boss)</t>
+          <t>Generated map renders correctly in Roblox Studio</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2835,7 +4566,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fortune system fully functional</t>
+          <t>Pre-generation: map ready before player enters battle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2847,22 +4578,10 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guild progression system</t>
+          <t>All Slice 1-4 systems work on the generated map</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Multiple quest types available</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -2871,12 +4590,115 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Balance pass: nothing feels obviously broken</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Seeded procedural generation, templates, regions, terrain assignment, elevation generation, connectivity, object placement, spawn zones, retries, map preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RegionGenerator.lua, future MapService/MapGenerator modules, template definitions, biome profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Main.server.lua, TemplateViewer.server.lua (if production)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Slices 1-3 (battle lifecycle, terrain rules), Slice 4 (deployment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Generated map state, tile/terrain/object data, spawn zones, connectivity validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Slice 2 terrain rules, Slice 4 deployment roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Slice 7 may provide terrain/prop/lighting/VFX assets. Slice 5 decides what is generated and where.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Generated map is playable, all tiles accessible, spawn zones valid, connectivity passes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>⬜ Not Started</t>
         </is>
       </c>
     </row>
@@ -2891,94 +4713,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Instructions</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Goal:</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fill with all designed content. Systems work — this is volume and variety.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marking progress</t>
+          <t>Done When:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Change ⬜ to ✅ in the Status column when a task is working in Roblox Studio</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Updating overview</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>When all items in a slice are ✅, update Status Overview and fill in the Completed date</t>
+          <t>20+ battles without repeating. Biomes feel distinct. Different builds create different playstyles.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Starting new session</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tell AI: "Read my game docs in D:\AI\Projects\CTRBLXAI\docs. Check the roadmap for where I am."</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>One slice = multiple sessions</t>
+          <t>All 15 Races implemented with passives and growth rates</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Each slice may take many chat sessions. That's normal.</t>
+          <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Order matters</t>
+          <t>All 15 Doctrines implemented with stat packages and skills</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Don't skip ahead. Later slices depend on earlier ones working.</t>
+          <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Notes column</t>
+          <t>Full Skill catalog loaded (all entries from Game Rules)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Track issues, decisions, or things to revisit.</t>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Full Augment catalog loaded (all Active entries)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All conventional weapon archetypes (15 types)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>All status effects (damage, control, buff/state)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>All 8 templates (T01-T08) for map generation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>All biomes (Plains through Beach — 12 total)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>All terrain types with transformations working</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>All map objects with interactions</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Encounter generation: different enemies per biome</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Battle conditions active (Rain, Thunderstorm, Heatwave, etc.)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Loot tables tuned per source (Normal, Elite, Boss)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fortune system fully functional</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guild progression system</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Multiple quest types available</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Balance pass: nothing feels obviously broken</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Full content catalogs, recruitment, tavern/upgrades, guild management, blacksmith, skill/doctrine/augment management workflows, quests, dispatch, explore, campaign progression, encounters, battle conditions, economy, full integration, balance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Future RecruitmentService, TavernService, GuildService, BlacksmithService, QuestService, DispatchService, ExploreService, ProgressionService modules</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Main.server.lua</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Slice 4 (persistence, inventory, equipment, loadouts), Slices 1-3 (combat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Public Contracts Provided</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Recruitment, tavern, guild, blacksmith, quest, dispatch, explore, progression APIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Public Contracts Consumed</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Slice 4 persistence/inventory/equipment APIs, Slices 1-3 combat APIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Must not rewrite Slice 4 save, inventory, or equipment internals. Slice 7 owns only visual presentation of these systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Full game loop: recruit → equip → quest → battle → reward → progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>⬜ Not Started</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -797,7 +797,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -1012,7 +1011,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -1020,7 +1018,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -1266,7 +1263,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1349,7 +1345,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1391,7 +1386,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -1488,7 +1482,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -1552,7 +1545,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
@@ -1560,7 +1552,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -1652,7 +1643,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -1828,7 +1818,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -1846,7 +1835,6 @@
         </is>
       </c>
     </row>
-    <row r="98"/>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
@@ -1983,7 +1971,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2005,7 +1992,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -2098,7 +2084,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -2250,7 +2235,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -2272,7 +2256,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -2350,7 +2333,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -3131,6 +3113,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3297,6 +3280,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -3312,7 +3296,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Terrain movement, elevation, Jump, movement pathing, blocking, target geometry, range, battlefield legality</t>
+          <t>Terrain movement, elevation, Jump, pathing, blocking, target geometry, range, battlefield legality, displacement/push physics (collision, fall damage)</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3308,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TargetingService.lua, TileDefinitions.lua</t>
+          <t>TargetingService.lua, TileDefinitions.lua, DisplacementService.lua</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3344,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Movement candidates, target candidates, range validation, elevation data, Jump/pathing APIs</t>
+          <t>Movement candidates, target candidates, range validation, elevation data, Jump/pathing APIs, displacement resolution (push/knockback, collision, fall damage)</t>
         </is>
       </c>
     </row>
@@ -3455,6 +3439,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3778,6 +3763,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -3793,7 +3779,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Client command submission, server command validation, Skills, AOE/patterns, MP/action costs, statuses, channeling/activation, combat resolution, trigger safety, skill-using AI, Guard</t>
+          <t>Client command submission, server validation, Skills, AOE/patterns, MP/costs, statuses, channeling, combat resolution, trigger safety, skill AI, Guard, Push command</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3827,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Command validation results, damage/healing outcomes, status application events, skill resolution pipeline, Guard mitigation</t>
+          <t>Command validation, damage/healing outcomes, status events, skill resolution, Guard mitigation, Push command validation and execution</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 6 - Content Expansion" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 7 - Visual Polish" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice 8 - Guild Base" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -654,6 +655,23 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Slice 8 — Guild Base and Out-of-Battle Systems</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>⬜ Not Started</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Guild Base hub, merchants, recruitment, quests, dispatch, explore, services, acquisitions</t>
         </is>
       </c>
     </row>
@@ -1949,6 +1967,1080 @@
           <t>🔄 In Progress — Stage 1 Desktop Checkpoint: e8dcc977</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Goal:</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>After returning from battle, the player can use the Guild Base to recruit and manage units, access services, improve facilities, select activities, purchase or earn progression items, and prepare for future battles.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Done When:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Guild Base hub is functional: recruitment, merchants, services, quests, dispatch, explore all operational with authoritative rules. All acquisitions persist through Slice 4 APIs.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Guild Base navigation and functional hub state</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Recruitment transactions</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tavern services</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guild progression (Guild XP, Guild Level)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Locked direction in DB: loot_progression / Guild Progression</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Facility upgrades</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Blacksmith services</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Locked direction: facility level, recipes, materials, no LUK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Out-of-battle merchants</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Locked direction: Guild/service progression, region, unlocks, no LUK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Skill management beyond basic persistent loadout storage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Doctrine management and acquisition</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Skill Card management and acquisition</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Augment Card management and acquisition</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Quest board</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quest types locked: bring-me, battle, arena, boss, protect, survive, defeat X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Locked: predetermined rewards shown before acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Explore</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Service costs and transactions</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Merchant prices and transactions</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unlocks and prerequisites</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Transition from Guild Base to battle preparation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>═══ ACQUIRABLE CONTENT ═══</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Equipment — battle loot, quest rewards, activity rewards, merchant purchases</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rules from Game Rules; definitions from Slice 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Consumables — battle loot, quest rewards, activity rewards, merchant purchases</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>140 items defined in consumable_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Doctrines — quest rewards, activity rewards, merchant purchases</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Duplicates valid per locked rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Skill Cards — quest rewards, activity rewards, merchant purchases</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Augment Cards — quest rewards, activity rewards, merchant purchases</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Acquisition eligibility, rarity, probabilities, prices per authoritative Game Rules</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Do not invent missing values</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>═══ ACQUISITION SOURCE BOUNDARY ═══</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Battle loot: generated and committed through Slice 4 reward + inventory transaction</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Slice 4 owned. Reward pipeline in reward_generation (10-step).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Quest/Dispatch/Explore/activity rewards: determined by Slice 8, handed to Slice 4 APIs</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Slice 8 validates → Slice 4 persists</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Merchant purchases: availability/price/validation = Slice 8; persistence = Slice 4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Town services use Guild Level, not LUK (locked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Content definitions: consumed from Slice 6 + Game Rules — Slice 8 does not redefine</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>═══ PERSISTENCE RULE ═══</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Slice 8 must NOT maintain a second inventory, roster, equipment, Skill, Doctrine, or Augment ownership database</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Acquisition flow: Slice 8 validates → Slice 8 produces result → Slice 4 records ownership → Slice 4 saves → Slice 7 presents</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unsuccessful transaction must not create or persist ownership</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>═══ EXISTING AUTHORITATIVE RULES IN DB ═══</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Loot Rarity Weights: Normal and Elite encounter tables (locked)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Reward Sequence: 6-step pipeline with rarity ceilings per source (locked)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Activities and Loot: drop chances, Fortune rules, categories, Doctrine/Skill/Augment reward directions (locked)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guild Progression: Guild XP, Guild Level gates merchants/recruitment/blacksmith/facilities (locked direction)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Elite Loot Rules: separate encounter and reward rules (locked)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gold Fortune: applies-to and doesn't-apply-to lists (locked)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Service Boundaries: Reward Service and other service scopes defined</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>service_boundaries table</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Consumable Framework + 140 items with full schemas</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>consumable_framework + consumable_items tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Reward Generation Pipeline: 10-step opportunity-to-commit pipeline</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>reward_generation table</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>═══ SPECIFIC VALUES NOT YET AUTHORED ═══</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Merchant inventories (which items, quantities)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Direction locked; specifics pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Merchant prices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Merchant refresh rates and behavior</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Recruitment pools and generation rules</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Direction locked; specifics pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Facility upgrade costs and tier progression</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Blacksmith recipes and material requirements</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Direction locked; specifics pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Quest reward tables (specific rewards per quest)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dispatch reward pools</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Predetermined rewards shown before acceptance (locked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Explore reward pools</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guild XP amounts per activity</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Low-level farming sharply reduced (locked direction); exact bands pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Elite encounter appearance rate</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>UNDEFINED</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Locked as rare random; exact rate pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Guild Base framework, merchants, purchases, recruitment, quest/activity rewards, Doctrine/Skill Card/Augment Card acquisition workflows, Tavern, Blacksmith, facility, Guild progression, management workflows, service costs, unlocks, battle-prep transition</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Slice 4 Dependencies</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Inventory ownership, roster ownership, equipment/loadout state, equip/unequip, save/load, adding acquired items to persistent inventory, restoring after rejoin, battle reward commitment, minimal functional Loadout Hub</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Slice 6 Dependencies</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Content catalogs: equipment, consumables, Doctrines, Skill Cards, Augment Cards</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Slice 7 Dependencies</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Guild Base visual presentation, merchant-screen layout, reward/acquisition presentation, item/Doctrine/Skill Card/Augment Card visual components, icons, portraits, rarity, themes, animations, VFX, responsive layout, UI sound</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Must not duplicate Slice 4 persistence, redefine Slice 6 content, or build Slice 7 presentation</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>═══ BLOCKERS AND STATUS ═══</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Locked frameworks and directions exist in DB — Slice 8 is not starting from zero</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>loot_progression, reward_generation, consumable_framework, service_boundaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Specific service values (prices, inventories, refresh, recipes, pools, costs) are not yet authored</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Design work needed for numerical values; locked directions provide the constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Slice 4 persistence APIs must be functional before Slice 8 can commit acquisitions</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Slice 6 content catalogs must exist before merchants can offer items</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Checkpoint Commit</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>⬜ Not Started</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3113,7 +4205,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3280,7 +4371,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -3439,7 +4529,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3763,7 +4852,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -3890,7 +4978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -3906,7 +4994,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Win battle → get loot. Go to menu, equip it. Save. Close Roblox, reopen — everything still there.</t>
+          <t>Win battle → get loot. Equip gear. Save. Close, reopen — progress persists. Slice 4 owns functional behavior and data contracts. Final visual polish belongs to Slice 7.</t>
         </is>
       </c>
     </row>
@@ -3918,7 +5006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Play multiple battles, collect loot, equip gear, save, close, reopen — progress intact. Different weapons change combat.</t>
+          <t>Functional lifecycle verified: battle → reward → persist → roster/inventory/equip → save → reload → confirm.</t>
         </is>
       </c>
     </row>
@@ -3942,7 +5030,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Battle end → reward screen shows loot (1-2 items)</t>
+          <t>Item generation works: rarity, random stat bonuses, BP validation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3954,7 +5042,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Item generation works: rarity, random stat bonuses, BP validation</t>
+          <t>Items committed to inventory after qualifying victory</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3966,7 +5054,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Items appear in inventory</t>
+          <t>Player can equip a weapon → unit stats change</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3978,7 +5066,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Menu UI: player can view roster of units</t>
+          <t>Equipment affects combat: different weapon = different damage/WT/range</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3990,7 +5078,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Menu UI: player can view inventory of items</t>
+          <t>Weapon WT applies to Basic Attack RT correctly</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4002,7 +5090,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Player can equip a weapon → unit stats change</t>
+          <t>Save writes to Roblox DataStore (compact numeric format)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4014,7 +5102,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Equipment affects combat: different weapon = different damage/WT/range</t>
+          <t>Load reads from DataStore and rebuilds full state</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4026,7 +5114,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Weapon WT applies to Basic Attack RT correctly</t>
+          <t>Save survives closing and reopening the game</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4038,7 +5126,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Save writes to Roblox DataStore (compact numeric format)</t>
+          <t>Save split: roster in key 1, inventory in key 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4050,7 +5138,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Load reads from DataStore and rebuilds full state</t>
+          <t>Lookup table approach: save stores IDs, game resolves to full data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4062,7 +5150,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Save survives closing and reopening the game</t>
+          <t>Doctrine equip works: stat package applies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4074,22 +5162,10 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Save split: roster in key 1, inventory in key 2</t>
+          <t>At least 3 weapon types feel different (Sword, Spear, Bow)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lookup table approach: save stores IDs, game resolves to full data</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -4098,38 +5174,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Doctrine equip works: stat package applies</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>--- Persistent HP/MP (bundled into Slice 4) ---</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>At least 3 weapon types feel different (Sword, Spear, Bow)</t>
+          <t>UnitSchema accepts persistent HP/MP instead of defaulting to full</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>⬜</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pass currentHp/currentMp from save state</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MP Regen system: accumulator + CT-based tick</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GameConstants + BattleCoordinator</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- Persistent HP/MP (bundled into Slice 4) ---</t>
+          <t>Battle-end: persist final HP/MP + apply 35% recovery</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Main.server.lua hook</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UnitSchema accepts persistent HP/MP instead of defaulting to full</t>
+          <t>Battle-start: load persistent HP/MP from save state</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4139,195 +5242,1181 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pass currentHp/currentMp from save state</t>
+          <t>Main.server.lua</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MP Regen system: accumulator + CT-based tick</t>
+          <t>KO units get zero recovery, flagged in save</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>⬜</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GameConstants + BattleCoordinator</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Battle-end: persist final HP/MP + apply 35% recovery</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Main.server.lua hook</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Battle-start: load persistent HP/MP from save state</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Main.server.lua</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>KO units get zero recovery, flagged in save</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>═══ SLICE 4D — REWARDS, MANAGEMENT CONTRACTS, AND LOADOUT TRANSACTIONS ═══</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deployment UI shows current HP/MP before battle</t>
+          <t>Goal:</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>Winning a qualifying battle awards persistent loot exactly once. Player can retrieve authoritative roster, inventory, equipment, and deployment data and submit server-validated equip/unequip requests. Slice 4D establishes functional data and interaction contracts. Final layout, theme, cards, icons, animations, responsive presentation, and visual polish belong to Slice 7.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>═══ SLICE OWNERSHIP ═══</t>
+          <t>--- 4D.1 — Battle Reward Transaction ---</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Functional Scope</t>
+          <t>Qualifying-victory detection</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Persistent roster, inventory, equipment, core loadouts, Skill/Doctrine/Augment assignment, deployment, save/load, DataStore, persistent HP/MP, post-battle recovery, battle rewards, item generation</t>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Owned Module Group</t>
+          <t>Reward-opportunity creation + reward count</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SaveService.lua, PersistentStateService.lua, InventoryService.lua, EquipmentService.lua, ItemGenerator.lua</t>
+          <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shared Integration Modules</t>
+          <t>Rarity selection from authoritative runtime data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Main.server.lua, BattleEvents.lua, UnitSchema.lua</t>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Single runtime authority for loot rarity weights</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Protected Dependencies</t>
+          <t>Item Level source: per-enemy = enemy level</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Slices 1-3 (battle lifecycle, combat, targeting)</t>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Encounter-completion Item Level: UNRESOLVED — BLOCKER</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Public Contracts Provided</t>
+          <t>Item generation via ItemGenerator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Save/load API, inventory state, equipment profiles, deployment roster, persistent HP/MP, item generation</t>
+          <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Public Contracts Consumed</t>
+          <t>Inventory commitment before save export</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Slices 1-3 battle results, unit state, combat outcomes</t>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NON-ATOMIC: one item per call, no batch, no rollback</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Forbidden Changes</t>
+          <t>Duplicate-processing protection</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Slice 7 may provide visual components but must not own inventory, equipment, loadout, or save transactions</t>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Local boolean prototype only — not durable across rejoin</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Minimum Regression Gate</t>
+          <t>Save ordering: commit rewards → export → save</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equip changes stats, save persists, load rebuilds, item generation validates BP band, post-battle recovery applies</t>
+          <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Reward summary payload to client</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Failure reporting</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>--- 4D.2 — Reward Presentation Contract ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Reward-summary payload (ownership committed before display)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Continue intent + Skip intent</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Functional completion state + destination after Continue</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PRESENTATION DEPENDENCY: Victory banner, reward cards, rarity glow, reveal animation, Continue/Skip buttons, timing, responsive layout, UI sound, VFX</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SLICE 7</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Slice 7 owned — do not build inside Slice 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>--- 4D.3 — Roster Data Contract ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Owned unit list with full persistent state (HP/MP/KO/equipment/doctrine/skills/augments/deployment)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Functional unit-selection intent</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PRESENTATION DEPENDENCY: Unit-card layout, HP/MP bars, KO icon, portraits, responsive roster layout</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SLICE 7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Slice 7 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>--- 4D.4 — Inventory Data Contract ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Complete item instances (identity, level, rarity, stats, bonuses, passives, equipped state)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Functional filter/sort values + item-selection intent</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PRESENTATION DEPENDENCY: Item-grid, item-card, icons, rarity borders, detail layout, filter/sort controls</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SLICE 7</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Slice 7 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>--- 4D.5 — Equip/Unequip Transaction ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Server-validated equip/unequip (ownership, slot, handedness, legality)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Off-hand clearing, duplicate prevention, loadout legality</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Stat rebuild after successful mutation</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Exactly once</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Before-and-after authoritative values for comparison</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Slice 4 supplies; Slice 7 presents</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Persistence after successful mutation</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PRESENTATION DEPENDENCY: Slot layout, comparison display, stat-delta colors, confirm/back, error tooltips</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SLICE 7</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Slice 7 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>--- 4D.6 — Deployment Resource Data Contract ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Persistent HP/MP/KO, deployment eligibility, functional warning/unavailable reason</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Deployment selection intent</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PRESENTATION DEPENDENCY: Resource bars, colors, warning presentation, KO symbol, responsive layout</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SLICE 7</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Slice 7 owned — warnings inform but do not block unless Game Rules defines restriction</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>--- 4D.7 — Functional Controller Integration ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Client controllers: request roster/inventory/equipment data, send equip/Continue/Skip intent</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Slice 4 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Controllers supply normalized data to Slice 7 views</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Controllers must not: define themes, position panels, hardcode rarity colors, own animations, calculate gameplay, bypass server</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Integrate with existing Slice 7 presentation APIs where available</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Record missing Slice 7 views as dependencies</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>═══ IMPLEMENTATION ORDER ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1. Resolve encounter-completion Reward Item Level authority</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Must be resolved before step 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2. Trace and lock post-battle transition contract</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3. Create one runtime authority for Loot Rarity Weights</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4. Implement RewardService transaction + duplicate guard</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5. Integrate reward commitment before save export</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6. Add reward-summary and post-battle functional events</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7. Implement roster and inventory data contracts</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8. Implement equip/unequip transaction events</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>9. Implement deployment resource data contract</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>10. Implement functional client controllers</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>11. Integrate with existing Slice 7 presentation where available</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>12. Record missing Slice 7 views as dependencies</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13. Run Slice 4D functional UAT</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14. Continue to Slice 4E integration and persistence hardening</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>═══ SLICE 4D COMPLETION GATE ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FUNCTIONAL:</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Qualifying victory creates one reward transaction</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Rewards committed exactly once, enter inventory before export</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Save payload contains complete awarded item identities</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Future load restores awarded items from persistent storage</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Roster data matches authoritative persistent unit state</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Inventory data matches authoritative item instances</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Equip/unequip server validated, stats rebuilt exactly once, persisted</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Deployment data displays authoritative resources and KO state</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Client cannot mutate inventory or equipment directly</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>No duplicate reward/recovery/save/equipment processing</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>No completed Slice 1/2/3/5/7 behavior modified without approved compatibility change</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PRESENTATION:</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Functional controllers expose required display data</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Existing Slice 7 components consumed where available</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Missing Slice 7 views recorded as dependencies</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Slice 4 does not create final layout/theme/animation/asset systems</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>═══ CURRENT BLOCKERS AND OPEN DECISIONS ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>BLOCKER 1: Encounter-completion Reward Item Level source is UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Per-enemy = enemy level (locked). Encounter-completion = NOT DEFINED. Do not implement until resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>BLOCKER 2: Post-battle functional transition not implemented</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BattleEnded fires before reward/save. Ordering among cleanup→reward display→Continue→menu must be defined. Slice 4 owns sequencing; Slice 7 owns visual transition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>OPEN RISK: Non-atomic multi-item reward commitment</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>One item per call, no batch, no rollback. Accept with failure handling or add batch operation — decision pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>OPEN RISK: Reward idempotency limited to prototype</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Local boolean guard only. No battleId. Does not survive rejoin. Durable identity needed for multi-battle/reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>VERDICT: READY WITH BLOCKERS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Reward transaction work may continue only after Item Level decision is approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>═══ SLICE OWNERSHIP ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Functional Scope</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Persistent roster, inventory, equipment, loadouts, Skill/Doctrine/Augment persistence, deployment, persistent HP/MP, KO, save/load, DataStore, battle rewards, server-authoritative validation, functional client controllers, data contracts, intent and response events</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Owned Module Group</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SaveService.lua, PersistentStateService.lua, InventoryService.lua, EquipmentService.lua, ItemGenerator.lua, RewardService.lua (PLANNED), future functional controllers</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Shared Integration Modules</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Main.server.lua, BattleEvents.lua, UnitSchema.lua — smallest diff, explicit purpose, no unrelated cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Protected Dependencies</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Slices 1-3 (battle lifecycle, combat, targeting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Slice 7 Presentation Dependencies</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Reward view, roster view, inventory view, equipment comparison view, deployment resource view — all Slice 7 owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Slice 7 Protected Files</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BattleHUD, Theme, UIConstants, UIFormatting, UIComponents, UILayoutCoordinator, UIController, UnitInspectorPanel, asset/animation/VFX/audio registries</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Forbidden Changes</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Slice 4 must not create visual design systems, bypass Slice 7 themes/layouts, or own final presentation. If Slice 7 view missing: record dependency, continue functional work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Minimum Regression Gate</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Equip changes stats, save persists, load rebuilds, item generation validates BP, rewards commit once, no Slice 1/2/3/7 regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Checkpoint Commit</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>⬜ In Progress</t>
         </is>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -1993,7 +1993,6 @@
           <t>After returning from battle, the player can use the Guild Base to recruit and manage units, access services, improve facilities, select activities, purchase or earn progression items, and prepare for future battles.</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2006,13 +2005,8 @@
           <t>Guild Base hub is functional: recruitment, merchants, services, quests, dispatch, explore all operational with authoritative rules. All acquisitions persist through Slice 4 APIs.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -2041,7 +2035,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2054,7 +2047,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2067,7 +2059,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2097,7 +2088,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2144,7 +2134,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2157,7 +2146,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2170,7 +2158,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2183,7 +2170,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2230,7 +2216,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2243,7 +2228,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2256,7 +2240,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2269,7 +2252,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2282,21 +2264,14 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>═══ ACQUIRABLE CONTENT ═══</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2360,7 +2335,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2373,7 +2347,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2392,19 +2365,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>═══ ACQUISITION SOURCE BOUNDARY ═══</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2468,21 +2435,14 @@
           <t>RULE</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>═══ PERSISTENCE RULE ═══</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2495,7 +2455,6 @@
           <t>RULE</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2508,7 +2467,6 @@
           <t>RULE</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2521,21 +2479,14 @@
           <t>RULE</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>═══ EXISTING AUTHORITATIVE RULES IN DB ═══</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2690,19 +2641,13 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>═══ SPECIFIC VALUES NOT YET AUTHORED ═══</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2732,7 +2677,6 @@
           <t>UNDEFINED</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2745,7 +2689,6 @@
           <t>UNDEFINED</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2775,7 +2718,6 @@
           <t>UNDEFINED</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2805,7 +2747,6 @@
           <t>UNDEFINED</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2835,7 +2776,6 @@
           <t>UNDEFINED</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2871,19 +2811,13 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
           <t>═══ SLICE OWNERSHIP ═══</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2896,7 +2830,6 @@
           <t>Guild Base framework, merchants, purchases, recruitment, quest/activity rewards, Doctrine/Skill Card/Augment Card acquisition workflows, Tavern, Blacksmith, facility, Guild progression, management workflows, service costs, unlocks, battle-prep transition</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2909,7 +2842,6 @@
           <t>Inventory ownership, roster ownership, equipment/loadout state, equip/unequip, save/load, adding acquired items to persistent inventory, restoring after rejoin, battle reward commitment, minimal functional Loadout Hub</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2922,7 +2854,6 @@
           <t>Content catalogs: equipment, consumables, Doctrines, Skill Cards, Augment Cards</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2935,7 +2866,6 @@
           <t>Guild Base visual presentation, merchant-screen layout, reward/acquisition presentation, item/Doctrine/Skill Card/Augment Card visual components, icons, portraits, rarity, themes, animations, VFX, responsive layout, UI sound</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2948,21 +2878,14 @@
           <t>Must not duplicate Slice 4 persistence, redefine Slice 6 content, or build Slice 7 presentation</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
           <t>═══ BLOCKERS AND STATUS ═══</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3009,7 +2932,6 @@
           <t>DEP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3022,13 +2944,8 @@
           <t>DEP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -3040,7 +2957,6 @@
           <t>⬜ Not Started</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5010,6 +4926,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5035,7 +4952,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5047,7 +4964,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5059,7 +4976,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5071,7 +4988,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5000,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5012,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5024,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5036,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5048,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5060,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5072,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5167,10 +5084,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -5186,7 +5104,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5203,7 +5121,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5220,7 +5138,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5237,7 +5155,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5254,10 +5172,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -5265,6 +5184,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -5277,6 +5197,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -5292,7 +5213,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5309,7 +5230,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5242,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5338,7 +5259,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5355,7 +5276,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5288,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5384,7 +5305,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5401,7 +5322,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5334,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5425,10 +5346,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -5444,7 +5366,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5461,7 +5383,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5478,7 +5400,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5495,7 +5417,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLICE 7</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5504,6 +5426,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -5519,7 +5442,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5536,7 +5459,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5471,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SLICE 7</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5557,6 +5480,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -5572,7 +5496,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5589,7 +5513,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5525,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SLICE 7</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5610,6 +5534,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -5625,7 +5550,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5642,7 +5567,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5579,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5671,7 +5596,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5688,7 +5613,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5625,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SLICE 7</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5709,6 +5634,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -5724,7 +5650,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5741,7 +5667,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5679,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SLICE 7</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5762,6 +5688,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
@@ -5777,7 +5704,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5794,7 +5721,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5750,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5762,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
+          <t>⏭️ Slice 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -5871,7 +5799,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5811,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5823,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5835,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5847,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5859,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5871,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5883,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5895,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5907,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5919,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
     </row>
@@ -6003,7 +5931,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6015,10 +5943,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -6041,7 +5970,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6053,7 +5982,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6065,7 +5994,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6006,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6018,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6030,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6042,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6054,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6066,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6078,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6090,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6109,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6121,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6133,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⏭️ Slice 7</t>
         </is>
       </c>
     </row>
@@ -6220,6 +6149,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -6295,18 +6225,20 @@
         </is>
       </c>
     </row>
+    <row r="117"/>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>VERDICT: READY WITH BLOCKERS</t>
+          <t>VERDICT: SLICE 4 FUNCTIONALLY COMPLETE (2026-08-31)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Reward transaction work may continue only after Item Level decision is approved.</t>
-        </is>
-      </c>
-    </row>
+          <t>Visual presentation deferred to Slice 7. Map Level placeholder awaits Slice 5. Doctrine Break/Augment attachment unassigned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -6418,7 +6350,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>⬜ In Progress</t>
+          <t>✅ Complete (2026-08-31)</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -788,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,6 +1967,787 @@
           <t>🔄 In Progress — Stage 1 Desktop Checkpoint: e8dcc977</t>
         </is>
       </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>═══ STAGE 2A: ROSTER AND UNIT LOADOUT PRESENTATION ═══</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Goal:</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Three-tab Loadout Hub (Info / Equipment / Skills) with persistent unit header, responsive layout, Theme-consistent presentation. Full spec in DB: loadout_ui_spec (59 rules).</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>--- Shared Navigation ---</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Three tabs at top: INFO | EQUIPMENT | SKILLS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Aligned beside Roblox system controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Persistent unit header: portrait, name, level, race, doctrine, 3x2 stat grid</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Upper-right on all tabs, compact</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Previous/next unit controls + tap-portrait unit selector</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Management selection only — no battle state change</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Unit switching preserves tab, refreshes all data, clears stale selections</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Pending-change guard on unit switch (confirm/cancel/discard)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>--- Info Tab ---</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Primary stats with breakdown (base, allocation, equipment, doctrine)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>STR INT DEX / AGI VIT LUK</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Stat allocation controls (only in Info)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>No respec — Slice 7 must not implement</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Secondary stats display with authoritative breakdown on select</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>No Critical Rate, Critical Damage, Evasion</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Race info: icon, name, growth rates, Race Perk, Race Drawback</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Separate labels from Unit Perk/Drawback</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Generated unit traits: one Perk, one Drawback</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Doctrine summary (display-only, managed from Equipment)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Unit records (only when authoritative data exists)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>--- Equipment Tab ---</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Inventory grid (left) + loadout (right) layout</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Square item cards, scrollable</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Complete loadout: MainHand, OffHand, Head, Torso, Arms, Legs, Accessory, 6 Consumable slots, Doctrine</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Off-Hand disabled when 2H equipped</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Consumable slots 1-3 usable, 4-6 visible locked with explanation</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Doctrine: mandatory, swap-only, cannot be empty or unequipped</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Item-type filters, rarity filter, sorting, search</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Item selection → comparison → equip/replace/swap transaction</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BP never shown in any player-facing UI</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>--- Equipment Comparison ---</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Current vs selected, only changed values</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Colors reflect gameplay consequence, not just math sign</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Authoritative before-and-after from Slice 4 — no independent calculation</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>--- Doctrine Comparison ---</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Swap Doctrine only (no Unequip). Warn if Doctrine Skill in Slot 1 affected</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>--- Skills Tab ---</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Five Skill rows: slot, icon, name, effect, MP, RT, 2 augment slots each</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Slot 1: Doctrine Skill (3 choices from doctrine, player selects one)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cannot accept normal Skill Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Slots 2-4: Skill Cards with 2 Augment slots each</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Slot 5: visible locked — 'Locked by First Race Evolution'</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Skill Card + Augment Card inventory with subtabs, stacking</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Skill Card details: full authoritative fields, formulas displayed not evaluated</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Augment Card details: compatibility from functional system, modified costs shown</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Filters: type, tags, element, compatibility</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>--- Interaction ---</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Desktop: drag-and-drop + click-to-select for Skills/Augments</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mobile: tap → highlight destinations → tap destination → preview → confirm</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Drag must not be only method</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Pending change preview before all commits</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>--- Responsive ---</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Mobile-first layout, desktop expanded</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Roblox controls unobstructed, tabs at top, no full rebuild on switch</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>--- Loadout Presentation Completion Gate ---</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Three tabs consistent, Roblox controls clear, unit switching works</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Info: accurate stats, allocation only in Info, no nonexistent stats</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Equipment: square cards, no BP, accurate comparison, doctrine swap-only</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Skills: doctrine skill slot 1, skill cards 2-4, locked slot 5, augment slots</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Mobile tap-based management works, desktop drag works</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Pending changes cannot be silently lost</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>No Slice 7 interface calculates authoritative gameplay values</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Save and reload preserve all committed loadout changes</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2006,7 +2787,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -2265,7 +3045,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -2365,7 +3144,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -2436,7 +3214,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -2480,7 +3257,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -2641,7 +3417,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -2811,7 +3586,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -2879,7 +3653,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
@@ -2945,7 +3718,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -4926,7 +5698,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5088,7 +5859,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -5176,7 +5946,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -5184,7 +5953,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -5197,7 +5965,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -5350,7 +6117,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -5426,7 +6192,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -5480,7 +6245,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -5534,7 +6298,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -5634,7 +6397,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -5688,7 +6450,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
@@ -5766,7 +6527,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -5947,7 +6707,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -6149,7 +6908,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -6225,7 +6983,6 @@
         </is>
       </c>
     </row>
-    <row r="117"/>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
@@ -6238,7 +6995,6 @@
         </is>
       </c>
     </row>
-    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>

--- a/docs/CTRBLXAI_Development_Roadmap.xlsx
+++ b/docs/CTRBLXAI_Development_Roadmap.xlsx
@@ -589,7 +589,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>⬜ Not started</t>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -649,7 +659,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>🔄 In Progress — Stage 1 Desktop Checkpoint Verified</t>
+          <t>🔄 In Progress — Stage 1 Complete, Stage 2 (Battle UI + Loadout) In Progress</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -788,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,6 +825,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -948,7 +959,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BattleHUD.lua expanded from 37KB to 66KB; UpdateTimeline exists</t>
         </is>
       </c>
     </row>
@@ -960,7 +976,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BattleHUD.ShowSkillList/ShowSkillDetail exist</t>
         </is>
       </c>
     </row>
@@ -972,7 +993,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>showDamageText/showFloatingText exist in BattleVisualClient</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1027,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LoadoutScreen.lua (76KB) created; LoadoutController.client.lua exists</t>
         </is>
       </c>
     </row>
@@ -1029,6 +1060,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -1036,6 +1068,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -1281,6 +1314,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1363,6 +1397,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1404,6 +1439,7 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -1500,6 +1536,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -1563,6 +1600,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
@@ -1570,6 +1608,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -1661,6 +1700,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -1836,6 +1876,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -1853,6 +1894,7 @@
         </is>
       </c>
     </row>
+    <row r="98"/>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
@@ -1968,20 +2010,15 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
           <t>═══ STAGE 2A: ROSTER AND UNIT LOADOUT PRESENTATION ═══</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -1993,21 +2030,14 @@
           <t>Three-tab Loadout Hub (Info / Equipment / Skills) with persistent unit header, responsive layout, Theme-consistent presentation. Full spec in DB: loadout_ui_spec (59 rules).</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
           <t>--- Shared Navigation ---</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2017,12 +2047,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Aligned beside Roblox system controls</t>
+          <t>LoadoutScreen.lua implements tab structure</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2064,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Upper-right on all tabs, compact</t>
+          <t>LoadoutScreen.lua implements header</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2081,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Management selection only — no battle state change</t>
+          <t>LoadoutScreen.lua implements unit switching</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2101,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2084,21 +2113,14 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="120"/>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
           <t>--- Info Tab ---</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2179,7 +2201,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2192,7 +2213,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2205,21 +2225,14 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="129"/>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
           <t>--- Equipment Tab ---</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2229,12 +2242,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🔄</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Square item cards, scrollable</t>
+          <t>LoadoutScreen.lua implements inventory grid</t>
         </is>
       </c>
     </row>
@@ -2246,10 +2259,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>LoadoutScreen.lua implements equipment slots</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2262,7 +2279,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2275,7 +2291,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2288,7 +2303,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2298,10 +2312,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>LoadoutScreen.lua implements filters</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2311,10 +2329,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>LoadoutScreen.BuildItemDetail exists</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2333,19 +2355,13 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-    </row>
+    <row r="139"/>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
           <t>--- Equipment Comparison ---</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2381,19 +2397,13 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-    </row>
+    <row r="143"/>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
           <t>--- Doctrine Comparison ---</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2406,21 +2416,14 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="146"/>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
           <t>--- Skills Tab ---</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2433,7 +2436,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2463,7 +2465,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2476,7 +2477,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2489,7 +2489,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2502,7 +2501,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2515,7 +2513,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2528,21 +2525,14 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr"/>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="156"/>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
           <t>--- Interaction ---</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2555,7 +2545,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2585,21 +2574,14 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
           <t>--- Responsive ---</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2612,7 +2594,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2631,19 +2612,13 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-    </row>
+    <row r="165"/>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
           <t>--- Loadout Presentation Completion Gate ---</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2656,7 +2631,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2669,7 +2643,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2682,7 +2655,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2695,7 +2667,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2708,7 +2679,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2721,7 +2691,6 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2734,7 +2703,6 @@
           <t>RULE</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2747,7 +2715,149 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>═══ STAGE 2B: BATTLE HUD EXPANSION (tracked post-audit) ═══</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>BattleHUD.lua expanded to 66KB (from 37KB baseline)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Major expansion: actor/target cards, skill list, damage preview, tile info, battle log, phase display, tooltips, confirm bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Theme.lua expanded to 20KB (from 7KB baseline)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Expanded color palette, rarity colors, spacing tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BattleVisualClient.lua expanded to 83KB (from 62KB baseline)</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>LoadoutScreen integration, expanded event handlers</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>UnitInspectorPanel.lua at 24KB</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3-tab inspector (Stats/Equipment/Skills)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>--- New Modules Created ---</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>LoadoutScreen.lua (76KB) — full loadout UI implementation</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Slice 7 Stage 2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>MockLoadoutData.lua (25KB) — test data for loadout development</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Development aid</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>LoadoutController.client.lua (2KB) — entry point, L key toggle</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5185,7 +5295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5652,6 +5762,753 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>Completed 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>═══ SLICE 3 FOUNDATION EXPANSION (post-completion) ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>--- Phase 1: Status Definitions ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GameConstants.STATUSES expanded from 4 → 36 entries (all DB statuses)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Includes Sleep, Silence, Stun, Petrify, Haste, Wet, Frozen, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>--- Phase 2: StatusService Expansion ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>StatusService.IsActionBlocked exists (Silence→skills, Disarmed→attack, Pinned→move)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sleep/Stun/Petrify blocking implemented; Disarmed/Pinned referenced but not fully tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Turn-skipping statuses (Sleep, Petrify, Stun) in BattleCoordinator</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Needs verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hard CC removes Guard on application</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sleep/Petrify should remove Guard — needs verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Status tick behaviors beyond DoT (Haste RT mod, Regeneration, Weakened, etc.)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>36 statuses defined; most tick behaviors not yet in StatusService runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Reapplication rules per status</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DB defines per-status reapplication; StatusService may not enforce all</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>--- Phase 3: Element System ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Element tag extraction in CombatResolver</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Element extraction logic exists; full interaction chain incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Element→status triggers (Fire→Burn, Water→Wet, Ice+Wet→Frozen)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Element weakness/resistance multipliers</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Depends on Phase 5 race tags for full effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Healing element interactions (Holy vs Undead)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Depends on Phase 5 Undead tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>--- Phase 4: Status Immunity Framework ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Immunity check before status application</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No IsImmune check in StatusService.ApplyStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Race-tag immunities registered (Undead, Mechanical)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Debuff Resistance stat functional (VIT-based)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Still defaults to 1.0 in code</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>--- Phase 5: Race Tag Functional Effects ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Race tags stored on unit at creation</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>RaceData has tags; UnitSchema doesn't copy to unit.tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Undead: healing reversal, Holy×2, immunities</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Mechanical: WT+15%, immunities, Wet doubled</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Amphibious: water movement, Drowning immunity</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Blocked — no water tiles in combat</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Flying: permanent Flight</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Blocked — Flight status not fully implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Giant: melee elevation range, knockback</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Giant tag added to DB (2026-09-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>--- Phase 6: Race Passive Evaluation ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RacePassiveService.lua created with 8 query functions</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>6.4KB — integrated into CombatResolver, CommandService, TargetingService, EquipmentService</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Orc Bloodlust (below 50% HP → +15% damage)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>In RacePassiveService.GetDamageDealtModifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dwarf Stout Resilience (physical DR -10%, Move -1)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DR in GetDamageReceivedModifier, Move in GetMovementRangeModifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Fairy Fae Grace (AOE DR -25%, STR -15%)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DR in GetDamageReceivedModifier, STR in GetStatModifiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Golem Fortified Frame (Guard +20%, Move -1)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Guard in GetGuardMitigationBonus, Move in GetMovementRangeModifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Zombie Undying (Move -1)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Movement penalty applied; revive NOT implemented (no revive system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Elf Elven Focus (MP Cost -20%)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>In RacePassiveService.GetMpCostModifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Elf Jump +1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NOT applied — ComputeDerivedStats uses formula only, no race bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Goblin Basic Attack applies Poison</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GetBasicAttackStatus returns 'Poison'; needs CombatResolver integration verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Elemental Spirit elemental damage +30%/-30%</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>In GetDamageDealtModifier and GetDamageReceivedModifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Lich Arcane Corruption (Light damage received +50%)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>In GetDamageReceivedModifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Shadow Umbral Veil (elemental DR +10%; Hide pending)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DR applied; Hide-on-hit NOT implemented (no Hide status)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Titan CanEquip2HAsWith1H</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>In RacePassiveService and EquipmentService</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Vampire lifesteal (15%/5%)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NOT implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Human Adaptability (EXP +10%, +1 stat/3 levels)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Blocked — no leveling/EXP system</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Android Push→Pull</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Blocked — DisplacementService needs Pull mechanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Mermaid Tidecaller (water tile bonuses)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Blocked — no water tiles in combat</t>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>--- Phase 7: Content Registry Bridge ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SkillData.lua generated (89 skills from DB)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>118KB data file</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AugmentData.lua generated (102 augments from DB)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>91KB data file</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DoctrineData.lua generated (32 doctrines from DB)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>33KB data file</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Registry.lua facade (GetSkill/GetAugment/GetDoctrine)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Battle systems consume Content Registry instead of hardcoded GameConstants.SKILLS</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CommandService/CombatResolver still use 6 hardcoded skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Formula evaluator for SkillData string formulas</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
